--- a/Practica3/Cerchas_Data2.xlsx
+++ b/Practica3/Cerchas_Data2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\structural-analysis\Practica3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19564654-2B68-4C1F-9F02-9F0BABF221DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2CC176F-AE9A-4A6C-95FC-E45104F02985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="250" yWindow="10340" windowWidth="16470" windowHeight="10640" activeTab="1" xr2:uid="{A9B2917F-5BBF-4B69-8795-8861410B002C}"/>
+    <workbookView xWindow="250" yWindow="10240" windowWidth="16470" windowHeight="10640" activeTab="1" xr2:uid="{A9B2917F-5BBF-4B69-8795-8861410B002C}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Node</t>
   </si>
@@ -67,6 +67,15 @@
   </si>
   <si>
     <t>Node_right</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Section</t>
+  </si>
+  <si>
+    <t>Material</t>
   </si>
 </sst>
 </file>
@@ -727,21 +736,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{364BF6D1-5869-4B18-96BE-BD9DF8C11852}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>7</v>
       </c>
       <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -749,98 +767,179 @@
         <v>1</v>
       </c>
       <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>2</v>
       </c>
-      <c r="C3">
+      <c r="F3">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
         <v>3</v>
       </c>
-      <c r="C4">
+      <c r="F4">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
         <v>4</v>
       </c>
-      <c r="C5">
+      <c r="F5">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
         <v>5</v>
       </c>
-      <c r="C6">
+      <c r="F6">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
         <v>7</v>
       </c>
-      <c r="C7">
+      <c r="F7">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
         <v>8</v>
       </c>
-      <c r="C8">
+      <c r="F8">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
         <v>9</v>
       </c>
-      <c r="C9">
+      <c r="F9">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
         <v>10</v>
       </c>
-      <c r="C10">
+      <c r="F10">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -848,105 +947,195 @@
         <v>1</v>
       </c>
       <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
         <v>2</v>
       </c>
-      <c r="C12">
+      <c r="F12">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
         <v>2</v>
       </c>
-      <c r="C13">
+      <c r="F13">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
         <v>3</v>
       </c>
-      <c r="C14">
+      <c r="F14">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
         <v>3</v>
       </c>
-      <c r="C15">
+      <c r="F15">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
         <v>4</v>
       </c>
-      <c r="C16">
+      <c r="F16">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
         <v>4</v>
       </c>
-      <c r="C17">
+      <c r="F17">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
         <v>5</v>
       </c>
-      <c r="C18">
+      <c r="F18">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
         <v>5</v>
       </c>
-      <c r="C19">
+      <c r="F19">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
         <v>6</v>
       </c>
-      <c r="C20">
+      <c r="F20">
         <v>11</v>
       </c>
     </row>
